--- a/rsvp_forms/013_destination_information_night_rsvp_form--rsvp_forms.xlsx
+++ b/rsvp_forms/013_destination_information_night_rsvp_form--rsvp_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -518,7 +518,11 @@
           <t>Event Details</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide event name and date</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,10 +542,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travel Info</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Travel Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provide travel plans, including transportation and accommodation</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -556,15 +564,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>attendee_info</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Attendee Info</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide your name, email and phone number</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,18 +591,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rsvp_details</t>
+          <t>num_attendees</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RSVP Details</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Number of Attendees</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How many people are attending?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,15 +618,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Special Requests</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Is there any additional information you'd like to share?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,18 +645,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>confirm_rsvp</t>
+          <t>confirm_event</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Confirm RSVP</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Confirm Event Attendance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Have you confirmed your event attendance?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,15 +672,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>confirm_travel</t>
+          <t>travel_arrangements</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Confirm Travel</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Travel Arrangements</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please specify your travel arrangements</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -671,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>additional_info</t>
+          <t>add_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Info</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Is there any additional information you'd like to share?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -705,375 +737,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>event_details_1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Event Details 1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>event_details_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Event Details 2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>travel_details_1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Travel Details 1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>travel_info_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Travel Info 1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>travel_info_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Travel Info 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>travel_info_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Travel Info 3</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>travel_info_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Travel Info 4</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>travel_info_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Travel Info 5</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>travel_details_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Travel Details 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>travel_details_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Travel Details 3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>travel_details_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Travel Details 4</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>event_details_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Event Details 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>travel_info_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Travel Info 3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>travel_info_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Travel Info 4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>event_details_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Event Details 3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>travel_info_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Travel Info 1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
